--- a/rules/CORE-000929/negative/02/data/unit-test-coreid-CG0001-negative-2.xlsx
+++ b/rules/CORE-000929/negative/02/data/unit-test-coreid-CG0001-negative-2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/enrico/Work/core-contributor/rules/CORE-000929/negative/02/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B36C7B50-E036-FC45-BFFE-001B71EBFE96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27D225DD-BFE6-EF43-99AE-DB6CA7D47BC5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1260" yWindow="660" windowWidth="28980" windowHeight="18980" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1260" yWindow="660" windowWidth="28980" windowHeight="18980" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Library" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="56">
   <si>
     <t>Product</t>
   </si>
@@ -80,12 +80,6 @@
   </si>
   <si>
     <t>C117466</t>
-  </si>
-  <si>
-    <t>$domain_lib_ccode</t>
-  </si>
-  <si>
-    <t>list of DOMAIN CCODEs published as of sdtmct-2017-12-22 (predates EC/C117466, added 2018-03-30)</t>
   </si>
   <si>
     <t>STUDYID</t>
@@ -203,8 +197,16 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -232,8 +234,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -596,26 +599,26 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A1" t="s">
+      <c r="A1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="1" t="s">
         <v>15</v>
       </c>
     </row>
@@ -637,26 +640,6 @@
       </c>
       <c r="F2" t="s">
         <v>18</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A3">
-        <v>1</v>
-      </c>
-      <c r="B3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C3" t="s">
-        <v>14</v>
-      </c>
-      <c r="D3" t="s">
-        <v>16</v>
-      </c>
-      <c r="E3" t="s">
-        <v>19</v>
-      </c>
-      <c r="F3" t="s">
-        <v>20</v>
       </c>
     </row>
   </sheetData>
@@ -671,125 +654,125 @@
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C1" t="s">
         <v>21</v>
       </c>
-      <c r="B1" t="s">
+      <c r="D1" t="s">
         <v>22</v>
       </c>
-      <c r="C1" t="s">
+      <c r="E1" t="s">
         <v>23</v>
       </c>
-      <c r="D1" t="s">
+      <c r="F1" t="s">
         <v>24</v>
       </c>
-      <c r="E1" t="s">
+      <c r="G1" t="s">
         <v>25</v>
       </c>
-      <c r="F1" t="s">
+      <c r="H1" t="s">
         <v>26</v>
       </c>
-      <c r="G1" t="s">
+      <c r="I1" t="s">
         <v>27</v>
       </c>
-      <c r="H1" t="s">
+      <c r="J1" t="s">
         <v>28</v>
       </c>
-      <c r="I1" t="s">
+      <c r="K1" t="s">
         <v>29</v>
       </c>
-      <c r="J1" t="s">
+      <c r="L1" t="s">
         <v>30</v>
       </c>
-      <c r="K1" t="s">
+      <c r="M1" t="s">
         <v>31</v>
-      </c>
-      <c r="L1" t="s">
-        <v>32</v>
-      </c>
-      <c r="M1" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C2" t="s">
         <v>34</v>
       </c>
-      <c r="B2" t="s">
+      <c r="D2" t="s">
         <v>35</v>
       </c>
-      <c r="C2" t="s">
+      <c r="E2" t="s">
         <v>36</v>
       </c>
-      <c r="D2" t="s">
+      <c r="F2" t="s">
         <v>37</v>
       </c>
-      <c r="E2" t="s">
+      <c r="G2" t="s">
         <v>38</v>
       </c>
-      <c r="F2" t="s">
+      <c r="H2" t="s">
         <v>39</v>
       </c>
-      <c r="G2" t="s">
+      <c r="I2" t="s">
         <v>40</v>
       </c>
-      <c r="H2" t="s">
+      <c r="J2" t="s">
         <v>41</v>
       </c>
-      <c r="I2" t="s">
+      <c r="K2" t="s">
         <v>42</v>
       </c>
-      <c r="J2" t="s">
+      <c r="L2" t="s">
         <v>43</v>
       </c>
-      <c r="K2" t="s">
+      <c r="M2" t="s">
         <v>44</v>
-      </c>
-      <c r="L2" t="s">
-        <v>45</v>
-      </c>
-      <c r="M2" t="s">
-        <v>46</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D3" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="F3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="G3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="H3" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="I3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="J3" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="K3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="L3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="M3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.2">
@@ -835,84 +818,84 @@
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
+        <v>47</v>
+      </c>
+      <c r="B5" t="s">
+        <v>48</v>
+      </c>
+      <c r="C5" t="s">
         <v>49</v>
-      </c>
-      <c r="B5" t="s">
-        <v>50</v>
-      </c>
-      <c r="C5" t="s">
-        <v>51</v>
       </c>
       <c r="D5">
         <v>1</v>
       </c>
       <c r="E5" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="F5" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="G5" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="H5">
         <v>10</v>
       </c>
       <c r="I5" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="J5">
         <v>10</v>
       </c>
       <c r="K5" t="s">
+        <v>52</v>
+      </c>
+      <c r="L5" t="s">
+        <v>53</v>
+      </c>
+      <c r="M5" t="s">
         <v>54</v>
-      </c>
-      <c r="L5" t="s">
-        <v>55</v>
-      </c>
-      <c r="M5" t="s">
-        <v>56</v>
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
+        <v>47</v>
+      </c>
+      <c r="B6" t="s">
+        <v>48</v>
+      </c>
+      <c r="C6" t="s">
         <v>49</v>
-      </c>
-      <c r="B6" t="s">
-        <v>50</v>
-      </c>
-      <c r="C6" t="s">
-        <v>51</v>
       </c>
       <c r="D6">
         <v>2</v>
       </c>
       <c r="E6" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="F6" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="G6" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="H6">
         <v>10</v>
       </c>
       <c r="I6" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="J6">
         <v>10</v>
       </c>
       <c r="K6" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="L6" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="M6" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
   </sheetData>
